--- a/sources/roger_step10.xlsx
+++ b/sources/roger_step10.xlsx
@@ -1196,6 +1196,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>db0103c6-cf73-4aa7-a401-ed64ab6e9ada</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
           <t>db0103c6-cf73-4aa7-a401-ed64ab6e9ada</t>
@@ -1263,6 +1268,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>7e3f4889-cf90-455b-95d7-3806d4162f5d</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>7e3f4889-cf90-455b-95d7-3806d4162f5d</t>
@@ -1328,6 +1338,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>217906c3-5a77-4875-a8eb-dda3b710c248</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">

--- a/sources/roger_step10.xlsx
+++ b/sources/roger_step10.xlsx
@@ -417,39 +417,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD95"/>
+  <dimension ref="A1:AE95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="103" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col hidden="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col hidden="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="123" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="103" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col hidden="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col hidden="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="123" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
     <col width="38" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="38" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,130 +483,135 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -622,67 +628,67 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Animal Stone Head</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Animal Stone Head</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Can be Tech Rolled but damage stays the same.</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>9143abf6-cd5a-4b37-89d0-2e8666c2bc89</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>aa8d707c-d126-4fa0-9619-43abd3afb3c0</t>
         </is>
@@ -699,62 +705,62 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Power Bomb</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Power Bomb</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>294eed17-963a-4a4a-a268-6bdaf04bdb06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>6d037824-7004-4594-b806-66f867371ad3</t>
         </is>
@@ -771,62 +777,62 @@
           <t>db,db+1+2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>DDT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>DDT</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>d03f5907-f3e6-4a5e-b08f-2b50ac9317b8</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>6b877fe9-9c21-40f6-9a6d-a4c36a86f99e</t>
         </is>
@@ -843,62 +849,62 @@
           <t>db,f+2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Tombstone Piledriver</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Tombstone Piledriver</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>7676dbff-eb8d-4184-ad77-459412b4f4ae</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>33ced16d-6ef9-4239-9192-80480fad6aaa</t>
         </is>
@@ -915,67 +921,67 @@
           <t>f,hcf+1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Animal Swing</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Animal Swing</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Can be Tech Rolled to reduce damage by half.</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>4b0603d6-9a36-4ce7-baaf-250e6c10a1af</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>ec474938-0187-4f80-8e32-7d814a62f9c4</t>
         </is>
@@ -992,67 +998,67 @@
           <t>qcf+1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Animal Driver</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Animal Driver</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1_3+4</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>da80d61f-dd6c-4004-b592-c434c9896ac1</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>a3cffffb-b67d-487c-a88d-9d8c5a878e85</t>
         </is>
@@ -1069,72 +1075,72 @@
           <t>df+3+4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>15,45</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>15,45</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Duck</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Only throws in close range against a standing opponent. Cannot be escaped or blocked.</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>a0c33ca9-129b-4d27-9609-ace02ee97b03</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>e10f2f1e-2572-4b1a-a97f-7682ab8b0d63</t>
         </is>
@@ -1158,55 +1164,60 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Running Bulldog</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Running Bulldog</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>db0103c6-cf73-4aa7-a401-ed64ab6e9ada</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>db0103c6-cf73-4aa7-a401-ed64ab6e9ada</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1230,55 +1241,60 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Swinging DDT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Swinging DDT</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>7e3f4889-cf90-455b-95d7-3806d4162f5d</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>7e3f4889-cf90-455b-95d7-3806d4162f5d</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1302,55 +1318,60 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Reverse Neck Toss</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Reverse Neck Toss</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>217906c3-5a77-4875-a8eb-dda3b710c248</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>217906c3-5a77-4875-a8eb-dda3b710c248</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1387,130 +1408,135 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="K15" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R15" s="1" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S15" s="1" t="inlineStr">
+      <c r="T15" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T15" s="1" t="inlineStr">
+      <c r="U15" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U15" s="1" t="inlineStr">
+      <c r="V15" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V15" s="1" t="inlineStr">
+      <c r="W15" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W15" s="1" t="inlineStr">
+      <c r="X15" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X15" s="1" t="inlineStr">
+      <c r="Y15" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y15" s="1" t="inlineStr">
+      <c r="Z15" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z15" s="1" t="inlineStr">
+      <c r="AA15" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA15" s="1" t="inlineStr">
+      <c r="AB15" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB15" s="1" t="inlineStr">
+      <c r="AC15" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC15" s="1" t="inlineStr">
+      <c r="AD15" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD15" s="1" t="inlineStr">
+      <c r="AE15" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1527,82 +1553,82 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>1e0cf85c-22b6-46d7-81e5-411e27fe995f</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>aa681f6d-3880-44e4-8a92-631ccfb6c6e2</t>
         </is>
@@ -1619,82 +1645,82 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>2d42ef95-3f1d-472b-882d-51b165d49aa4</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>6a7ab77e-da4a-49ad-b45c-2ac04b1db27c</t>
         </is>
@@ -1711,36 +1737,31 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1758,35 +1779,40 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>fc7d1390-1cff-4294-b79b-80cf4f7ad9e6</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>697b553e-7d3d-4697-875b-2a054f82dbab</t>
         </is>
@@ -1803,46 +1829,41 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1850,35 +1871,40 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>5c29b2dc-c720-4470-b9c3-2530dd067d43</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>b038ac1c-32eb-4829-9c5b-fb55935b34d1</t>
         </is>
@@ -1895,82 +1921,82 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>cf8b1751-f202-48b1-8cd2-f98aaeeee95f</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>b95de222-23ef-4517-89a9-c369bef9f372</t>
         </is>
@@ -1987,82 +2013,82 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>811b87c1-8e4b-4aae-a361-e1c22f8940ac</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>8eee3a26-008a-47c1-9e3e-28fc064b9bba</t>
         </is>
@@ -2079,36 +2105,31 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>KD</t>
@@ -2126,35 +2147,40 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>4d89f457-7f65-47f5-8d67-21f67130eee4</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>458a3044-64ba-45ec-833d-5c86b703f616</t>
         </is>
@@ -2171,46 +2197,41 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>KD</t>
@@ -2218,35 +2239,40 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>a509da9a-3591-4525-a3fa-730cde6e2884</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>5efe37e1-8f37-4a07-95b0-a0b5ab7a93c3</t>
         </is>
@@ -2263,82 +2289,82 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>afe28f83-439a-46f4-b951-61f2a88b2957</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>b759497e-b67c-4365-a391-c6956261fdd8</t>
         </is>
@@ -2355,82 +2381,82 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>af1704c8-c6e9-434e-bcd0-9a6a11c177c2</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>ed2bd869-2846-4db3-98bc-a0de2b9e513d</t>
         </is>
@@ -2447,82 +2473,82 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>bdb7b0ba-8c75-4ef2-9634-da7d0397e318</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>f0f7de55-5c68-430d-ad31-cf2424d09d91</t>
         </is>
@@ -2539,82 +2565,82 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>89529e1a-6cb3-4fa0-8d7e-f0db9a413cd2</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>fd4df343-3664-47e3-82f0-387ba984dc45</t>
         </is>
@@ -2631,82 +2657,82 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>fb3cabf9-6618-4ff2-bfca-bdd38e6c6c40</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>bfb9cea6-49e1-4030-b270-130d503a5638</t>
         </is>
@@ -2723,82 +2749,82 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>7c6a0a91-4ccb-40ad-b054-05776c658d0d</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>48d52592-0315-44b8-a42f-b12351990d86</t>
         </is>
@@ -2815,82 +2841,82 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>3350a2d8-176c-4ab1-b3a3-f0a0ddf0bf7c</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>609ca5b5-4e9d-4b36-8586-c3d6e979427a</t>
         </is>
@@ -2907,82 +2933,82 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>1793e62a-1937-451e-9fe7-2c51b83b4781</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>72b76d53-1475-41ab-ad5f-63c672f20406</t>
         </is>
@@ -2999,82 +3025,82 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>af163443-22e9-49b0-b011-37e03fea2958</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>5d38ba75-3e85-4389-a65c-a8daa18ef88f</t>
         </is>
@@ -3091,46 +3117,41 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3138,35 +3159,40 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>037f689e-8c27-4cd6-95e7-b62125894448</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>05d75eb2-863f-459f-a7b9-298d9b178de1</t>
         </is>
@@ -3183,36 +3209,31 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3230,35 +3251,40 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>53cdd066-d620-4933-b3ac-c21936a4e0ed</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>6f1ded64-347f-432a-8a0d-01a795c68ba2</t>
         </is>
@@ -3275,82 +3301,82 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>a120b173-85fa-4f43-ac11-18d20f69e891</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>94ddbfa9-040b-4339-b20c-d0cb4215bea7</t>
         </is>
@@ -3367,46 +3393,41 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3414,35 +3435,40 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>abccd84e-c05e-4588-b689-b7477a776a0c</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>252a9af3-9d33-4964-907e-3e7abf22d10b</t>
         </is>
@@ -3459,82 +3485,82 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>05a182b1-f99b-4b4d-988c-9d24dfcff57a</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>fec74674-459e-4db8-8b3c-cf0efdd0c2c9</t>
         </is>
@@ -3551,82 +3577,82 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>6c49debc-c336-4b0a-8b06-e474f1482335</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>4442f7fe-b26d-4a65-b3aa-6351c6ecd52b</t>
         </is>
@@ -3643,82 +3669,82 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>624adefa-543d-4a07-a37a-014b088a780e</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>0c65b5f4-ddac-4ba9-803f-4d864475371e</t>
         </is>
@@ -3755,130 +3781,135 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
+      <c r="H42" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H42" s="1" t="inlineStr">
+      <c r="I42" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I42" s="1" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J42" s="1" t="inlineStr">
+      <c r="K42" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K42" s="1" t="inlineStr">
+      <c r="L42" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L42" s="1" t="inlineStr">
+      <c r="M42" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M42" s="1" t="inlineStr">
+      <c r="N42" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N42" s="1" t="inlineStr">
+      <c r="O42" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O42" s="1" t="inlineStr">
+      <c r="P42" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="Q42" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q42" s="1" t="inlineStr">
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R42" s="1" t="inlineStr">
+      <c r="S42" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S42" s="1" t="inlineStr">
+      <c r="T42" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T42" s="1" t="inlineStr">
+      <c r="U42" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U42" s="1" t="inlineStr">
+      <c r="V42" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V42" s="1" t="inlineStr">
+      <c r="W42" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W42" s="1" t="inlineStr">
+      <c r="X42" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X42" s="1" t="inlineStr">
+      <c r="Y42" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y42" s="1" t="inlineStr">
+      <c r="Z42" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z42" s="1" t="inlineStr">
+      <c r="AA42" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA42" s="1" t="inlineStr">
+      <c r="AB42" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB42" s="1" t="inlineStr">
+      <c r="AC42" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC42" s="1" t="inlineStr">
+      <c r="AD42" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD42" s="1" t="inlineStr">
+      <c r="AE42" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3895,92 +3926,92 @@
           <t>1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Double Punch - Upper</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Double Punch - Upper</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>+2 0 0</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+2 0 0</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>6,10,10</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>6,10,10</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>34eb26a1-1c17-4b1f-85a7-c58d8bd87cec</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>2a686d52-3647-43bb-99d9-27befae3991f</t>
         </is>
@@ -3997,56 +4028,51 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Elbow Sting</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Elbow Sting</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4054,40 +4080,45 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>GB SLDc</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>36759311-beb4-4bbe-b5c5-e9c87018aa6e</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>daee3b20-5f00-4748-ad72-5c5d9fb931f7</t>
         </is>
@@ -4104,46 +4135,41 @@
           <t>f,f,N+1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Animal Gigaton Punch</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Animal Gigaton Punch</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4161,35 +4187,40 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>14259c5a-ef00-4dda-a6f2-564866d40c34</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>26522da2-dbd2-427f-88bb-42e41009e86b</t>
         </is>
@@ -4206,46 +4237,41 @@
           <t>f,N,d,df+1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Animal Godfist</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Animal Godfist</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4263,35 +4289,40 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>4b1a4878-d959-4f0b-a83d-09ee264e8dc1</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>8c567cc4-228c-4ab2-84b2-c22a8fe6a069</t>
         </is>
@@ -4308,92 +4339,92 @@
           <t>d+1 ,N+2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Low Jab - Upper</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Low Jab - Upper</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-2 -9</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>-2 -9</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>sm</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>sm</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>2ec7108a-1e44-4672-94bf-bce20dc208ba</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>0e30304e-0233-4f65-89e9-2f59860e0964</t>
         </is>
@@ -4410,46 +4441,41 @@
           <t>f,N+1</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Rolling Animal Punch</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Rolling Animal Punch</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>+41</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+41</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4467,40 +4493,45 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>41b172f4-4096-4e61-aacb-e9465d14d08b</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>dcdde8b7-b16c-4195-85cd-b3088d2daa36</t>
         </is>
@@ -4517,97 +4548,97 @@
           <t>f,f+1 ,2 ,1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Animal Rush - Windmill Punch</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Animal Rush - Windmill Punch</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>+1 0 +1 -11 +23</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+1 0 +1 -11 +23</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+12 +11 +12 0 KD</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+12 +11 +12 0 KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>+12 +11 +12 0 KD</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>+12 +11 +12 0 KD</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>10,15,10,15,20</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>10,15,10,15,20</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>hhhhm</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>hhhhm</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>1f531185-e8d1-445d-82c2-79e92d4ec1d5</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>b8257840-eee6-4c57-b27e-7bb7c31c4ceb</t>
         </is>
@@ -4624,46 +4655,41 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Flying Cross Chop</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Flying Cross Chop</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>(-5_-25)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>(-5_-25)</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4681,45 +4707,50 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>h_l</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>h_l</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>Hits high at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>f4a41c9d-92c4-4b84-bf14-8c7943dfc79a</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>2d38653d-5b5f-4fcd-bf75-7f30cd4edd66</t>
         </is>
@@ -4736,97 +4767,97 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Animal Headbutt</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Animal Headbutt</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>KS GB</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>4d40eed7-683a-49b0-a516-7a0e5ed09f7a</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>cb2f5780-6dfe-4fdd-8bd7-b7baeea7cdbd</t>
         </is>
@@ -4850,44 +4881,44 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>f+1+2; uf+1+2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4905,40 +4936,45 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>dda9a159-0258-45c6-a260-7b9752f3eb8d</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>85bc9d1d-5f1e-4d3d-aec8-1d26b26c0600</t>
         </is>
@@ -4955,46 +4991,41 @@
           <t>FC+1+2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Animal Smash</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Animal Smash</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-25</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-25</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5012,35 +5043,40 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>b1148d23-92d5-4300-b9fc-d7d60392d6c9</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>45f6b231-0e95-4049-99c3-15d6d34d29f2</t>
         </is>
@@ -5057,46 +5093,41 @@
           <t>f,N,d,df+1+2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Delayed Animal Smash</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Delayed Animal Smash</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-25</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>-25</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5114,35 +5145,40 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>99723661-6aa8-49e1-b882-52427bdf97c8</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>27fe7720-38e5-489d-b4c1-26d2fcb86ff8</t>
         </is>
@@ -5159,92 +5195,92 @@
           <t>2 ,1</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Straight Right - Elbow</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Straight Right - Elbow</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>+6 +11</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>+6 +11</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>+6 +11</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>+6 +11</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>19a2d7ce-2a75-46ec-bb65-6129b313e47c</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>fcfd5381-7454-4faf-b10b-71a0eee43e52</t>
         </is>
@@ -5261,46 +5297,41 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Smash Upper</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Smash Upper</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5318,45 +5349,50 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>890377a5-299a-42ad-87ac-65b21be329ea</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>8425202a-0474-4e45-af1f-edbae2dc0167</t>
         </is>
@@ -5373,56 +5409,51 @@
           <t>f,f,N+2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Ground Smash</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Ground Smash</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5430,40 +5461,45 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>DSc</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>9544e56e-3a99-46ee-adac-433b8c1a6e12</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>02d5dc28-98e7-4c73-9e5e-461b162c8777</t>
         </is>
@@ -5480,46 +5516,41 @@
           <t>FC+df+2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Animal Upper</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Animal Upper</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5537,45 +5568,50 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>0280dd04-c66f-4e74-bae1-6767b93393bb</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>8fff1712-3f4d-4b13-b33f-ca8b1ba40bef</t>
         </is>
@@ -5599,60 +5635,65 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>u+2+4; uf+2+4</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Elbow Drop</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Elbow Drop</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>5a9b00c4-2121-431f-a40f-32aac2b5395d</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>d9f6d981-bb28-44b2-96aa-9f146fef4bed</t>
         </is>
@@ -5669,46 +5710,41 @@
           <t>db+3</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Tail Cutter</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Tail Cutter</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5726,40 +5762,45 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>ba94b611-89b9-412e-ba8a-4bcc27e8a1fa</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>e8394c95-3561-46b8-8344-63466385f745</t>
         </is>
@@ -5776,92 +5817,92 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Double Knee Drop</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Double Knee Drop</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>8a4dd235-e4dc-4a5d-978f-2ce89e1e9e8f</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>a62dd4ab-9d4b-4f9b-b1fe-e8dcc4a0b787</t>
         </is>
@@ -5878,26 +5919,21 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Delayed DROP Kick</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Delayed DROP Kick</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5915,40 +5951,45 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>d29df63f-c211-4c6e-84de-973a4f8b0afb</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>395408a0-5589-45bf-b709-5a69047b9c69</t>
         </is>
@@ -5965,36 +6006,31 @@
           <t>f,f+3+4</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Animal DROP Kick</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Animal DROP Kick</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6012,40 +6048,45 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>c25d811a-8b76-4db3-b78b-43f1ece4f2a4</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>6c04fb61-1cc9-4215-9395-44770535a665</t>
         </is>
@@ -6069,34 +6110,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>f,f,f+3+4</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Satellite DROP Kick</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Satellite DROP Kick</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6114,40 +6155,45 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>75c03d5f-bf8f-4b25-bd24-9da1c206b994</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>2d59d6fb-9adb-4ed0-8163-c548e610d1fe</t>
         </is>
@@ -6171,100 +6217,105 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>D,df+4,4,4</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>Ali Kicks</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Ali Kicks</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-29 -35 -35</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>-29 -35 -35</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>13_17,7,7</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>13_17,7,7</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>Damage is 13 when no second kick is buffered.</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>b135a5f4-6a14-48bb-85cc-8aa7802b5411</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>f8da0865-a62f-402e-b72d-b04394877396</t>
         </is>
@@ -6281,102 +6332,102 @@
           <t>d+3+4 ,4 ,4 ,4 ,4</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>– Extended Ali Kicks</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Ali Kicks – Extended Ali Kicks</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>x -35</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>-29 -35 -35 x -35</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>x +15</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>-13 -19 +6 x +15</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>x +15</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>-13 -19 +6 x +15</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>13_17,7,7,4,3</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>LLLLL</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>CH RC</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>Extended Ali Kicks can only be done if the 1st Ali Kick was a counter hit. Damage of the 3rd Kick will be 5 instead of 7.</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>d2520916-f29b-4e99-be7f-c845f4ad0c1e</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>d9ffdd1c-ebf5-4f4e-bb06-692d0e1994cb</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>b135a5f4-6a14-48bb-85cc-8aa7802b5411</t>
         </is>
@@ -6393,46 +6444,41 @@
           <t>b+3+4</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Lunge Animal Kick</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Lunge Animal Kick</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-65</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>-65</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6450,35 +6496,40 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>20793ef8-792a-4286-8632-d9e01684ac50</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>68d99b4a-d29f-4f0a-8d44-5339b761fa60</t>
         </is>
@@ -6495,77 +6546,77 @@
           <t>b+3+4~B</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Roll Back</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-65</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>30,-</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>fcc6c234-c91c-4367-8e4d-43254b56d550</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>9ddbbc92-b8f8-499f-ba50-b9aba23b94bc</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>20793ef8-792a-4286-8632-d9e01684ac50</t>
         </is>
@@ -6582,92 +6633,92 @@
           <t>b+3+4 ,3 ,4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>– Animal Kick Rush</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Animal Kick Rush</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-29 -29</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-65 -29 -29</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>KD -18 -18</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>KD -18 -18</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>17,17</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>30,17,17</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>32f07f4b-7ea1-4d72-9226-3c5f32c900fc</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>4416a641-dfeb-4138-ad92-3f9cdd0e3e85</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>20793ef8-792a-4286-8632-d9e01684ac50</t>
         </is>
@@ -6684,77 +6735,77 @@
           <t>b+3+4 ,3 ,4~B</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>–– Roll Back</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Animal Kick Rush – Roll Back</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>-65 -29 -29</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>KD -18 -18</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>KD -18 -18</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>30,17,17,-</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>mmm-</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>e13d27e9-f953-4946-899f-dd53f0f11529</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>b23cdada-4469-4cd3-8d53-bdc7b5ebe6d8</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AD70" t="inlineStr">
         <is>
           <t>32f07f4b-7ea1-4d72-9226-3c5f32c900fc</t>
         </is>
@@ -6771,92 +6822,92 @@
           <t>b+3+4 ,3 ,4 ,3 ,4</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>–– Animal Kick Rush</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Animal Kick Rush – Animal Kick Rush</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>-29 -29</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>-65 -29 -29 -29 -29</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>KD -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>KD -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>17,17</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>30,17,17,17,17</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>mmmmm</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>e2c8e655-63b1-4183-9ee5-6b6514937d17</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>b7d3b8a1-b382-44f5-b0cb-2484f91ecbdc</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>32f07f4b-7ea1-4d72-9226-3c5f32c900fc</t>
         </is>
@@ -6873,77 +6924,77 @@
           <t>b+3+4 ,3 ,4 ,3 ,4~B</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>––– Roll Back</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Animal Kick Rush – Animal Kick Rush – Roll Back</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>-65 -29 -29 -29 -29</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>KD -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>KD -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>30,17,17,17,17,-</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>mmmmm-</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>a2e4233a-ccc3-4b21-a5ea-b67e196358b4</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>5808aafc-90cc-4514-bb47-5a3c13f0c24d</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
+      <c r="AD72" t="inlineStr">
         <is>
           <t>e2c8e655-63b1-4183-9ee5-6b6514937d17</t>
         </is>
@@ -6960,92 +7011,92 @@
           <t>b+3+4 ,3 ,4 ,1</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>–– Rolling Animal</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Animal Kick Rush – Rolling Animal</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-59</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>-65 -29 -29 -59</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>-48</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>KD -18 -18 -48</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>-48</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>KD -18 -18 -48</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>30,17,17,-</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>mmm-</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>08b4077f-9605-40ae-af5e-0248b260d49c</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AC73" t="inlineStr">
         <is>
           <t>15fdfe8d-0658-4d37-8bcb-3955465b28dc</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
+      <c r="AD73" t="inlineStr">
         <is>
           <t>32f07f4b-7ea1-4d72-9226-3c5f32c900fc</t>
         </is>
@@ -7062,92 +7113,92 @@
           <t>b+3+4 ,3 ,4 ,1 ,3 ,4</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>––– Animal Kick Rush</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Animal Kick Rush – Rolling Animal – Animal Kick Rush</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>-29 -29</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>-65 -29 -29 -59 -29 -29</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>KD -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>17,17</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>30,17,17,-,17,17</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>mmm-mm</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>105a3531-644f-46e0-b2c0-cf7b5750419b</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AC74" t="inlineStr">
         <is>
           <t>7b9e728a-ea0a-4707-bb40-976df75bb3bb</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
+      <c r="AD74" t="inlineStr">
         <is>
           <t>08b4077f-9605-40ae-af5e-0248b260d49c</t>
         </is>
@@ -7164,77 +7215,77 @@
           <t>b+3+4 ,3 ,4 ,1 ,3 ,4~B</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>–––– Roll Back</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Animal Kick Rush – Rolling Animal – Animal Kick Rush – Roll Back</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>-65 -29 -29 -59 -29 -29</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>KD -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>KD -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>30,17,17,-,17,17,-</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>mmm-mm-</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>711aeb90-69b8-4a6a-a7af-f5b02a973f1b</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>b54e666a-26e9-4ae5-86e4-71a5081cc094</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="AD75" t="inlineStr">
         <is>
           <t>105a3531-644f-46e0-b2c0-cf7b5750419b</t>
         </is>
@@ -7251,92 +7302,92 @@
           <t>b+3+4 ,1</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>– Rolling Animal</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>-59</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>-65 -59</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>-48</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>KD -48</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>-48</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>KD -48</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>30,-</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>7b58ef3a-2d54-4b6c-9723-c23f75d4711c</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>21de2b9a-b3ab-476e-9739-4c09809641e7</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
+      <c r="AD76" t="inlineStr">
         <is>
           <t>20793ef8-792a-4286-8632-d9e01684ac50</t>
         </is>
@@ -7353,92 +7404,92 @@
           <t>b+3+4 ,1 ,3 ,4</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>–– Animal Kick Rush</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal – Animal Kick Rush</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>-29 -29</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>-65 -59 -29 -29</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>KD -48 -18 -18</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>KD -48 -18 -18</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>17,17</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>30,-,17,17</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>m-mm</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>2e6b3c96-2534-4143-84e3-64165e2edc96</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>ee2e270e-a455-422e-b25a-23219e92af4a</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>7b58ef3a-2d54-4b6c-9723-c23f75d4711c</t>
         </is>
@@ -7455,77 +7506,77 @@
           <t>b+3+4 ,1 ,3 ,4~B</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>––– Roll Back</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal – Animal Kick Rush – Roll Back</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>-65 -59 -29 -29</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>KD -48 -18 -18</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>KD -48 -18 -18</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>30,-,17,17,-</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>m-mm-</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>7d6af8c7-4552-43bc-882f-ed2deb0d3550</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>d301e1cf-5a9e-4cc2-95f5-bb9431941f21</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
+      <c r="AD78" t="inlineStr">
         <is>
           <t>2e6b3c96-2534-4143-84e3-64165e2edc96</t>
         </is>
@@ -7542,92 +7593,92 @@
           <t>b+3+4 ,1 ,3 ,4 ,3 ,4</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>––– Animal Kick Rush</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal – Animal Kick Rush – Animal Kick Rush</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-29 -29</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>-65 -59 -29 -29 -29 -29</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>17,17</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>30,-,17,17,17,17</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>m-mmmm</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>5151429e-9e51-4d0c-8a2f-1dac46230821</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>252cc083-60d1-4134-9c92-bca00fdb0890</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
+      <c r="AD79" t="inlineStr">
         <is>
           <t>2e6b3c96-2534-4143-84e3-64165e2edc96</t>
         </is>
@@ -7644,77 +7695,77 @@
           <t>b+3+4 ,1 ,3 ,4 ,3 ,4~B</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>–––– Roll Back</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal – Animal Kick Rush – Animal Kick Rush – Roll Back</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>-65 -59 -29 -29 -29 -29</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -18 -18</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>30,-,17,17,17,17,-</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>m-mmmm-</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>50a600d0-4e45-4ddb-b387-3ee88cce1893</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
+      <c r="AC80" t="inlineStr">
         <is>
           <t>b12e296c-7332-493e-ab4d-8920c24c0e61</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
+      <c r="AD80" t="inlineStr">
         <is>
           <t>5151429e-9e51-4d0c-8a2f-1dac46230821</t>
         </is>
@@ -7731,92 +7782,92 @@
           <t>b+3+4 ,1 ,3 ,4 ,1</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>––– Rolling Animal</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal – Animal Kick Rush – Rolling Animal</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>-59</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>-65 -59 -29 -29 -59</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>-48</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -48</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>-48</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -48</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>30,-,17,17,-</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>m-mm-</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>25704ef5-0c9b-49be-8d48-1c4d248b935f</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>9a0e5cc1-03d7-42fd-a2cf-3ac222eaf0b4</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
+      <c r="AD81" t="inlineStr">
         <is>
           <t>2e6b3c96-2534-4143-84e3-64165e2edc96</t>
         </is>
@@ -7833,92 +7884,92 @@
           <t>b+3+4 ,1 ,3 ,4 ,1 ,3 ,4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>–––– Animal Kick Rush</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal – Animal Kick Rush – Rolling Animal – Animal Kick Rush</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-29 -29</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>-65 -59 -29 -29 -59 -29 -29</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>-18 -18</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>17,17</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>30,-,17,17,-,17,17</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>m-mm-mm</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>3520a5b8-973a-4cdd-adcf-847254146e12</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AC82" t="inlineStr">
         <is>
           <t>192949b1-f677-4b6f-95c2-806524186352</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
+      <c r="AD82" t="inlineStr">
         <is>
           <t>25704ef5-0c9b-49be-8d48-1c4d248b935f</t>
         </is>
@@ -7935,77 +7986,77 @@
           <t>b+3+4 ,1 ,3 ,4 ,1 ,3 ,4~B</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>––––– Roll Back</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Lunge Animal Kick – Rolling Animal – Animal Kick Rush – Rolling Animal – Animal Kick Rush – Roll Back</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>-65 -59 -29 -29 -59 -29 -29</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>KD -48 -18 -18 -48 -18 -18</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>30,-,17,17,-,17,17,-</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>m-mm-mm-</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>a32c1ee8-04aa-4583-ad85-2d405313376d</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="AC83" t="inlineStr">
         <is>
           <t>65445955-0a55-4fa3-a03f-de75d541be30</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
+      <c r="AD83" t="inlineStr">
         <is>
           <t>3520a5b8-973a-4cdd-adcf-847254146e12</t>
         </is>
@@ -8022,46 +8073,41 @@
           <t>u+3+4</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Jumping Animal Sweep</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Jumping Animal Sweep</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>-42</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>-42</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8079,40 +8125,45 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="V84" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>8b8d4dc2-6fb4-4580-8542-3abc3c013dea</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
+      <c r="AC84" t="inlineStr">
         <is>
           <t>eedf4d37-5ae2-4bea-b9b5-7d6d1b129c4c</t>
         </is>
@@ -8129,36 +8180,31 @@
           <t>df+3+4</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8176,40 +8222,45 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>Will throw when hitting a standing opponent. Damage of the throw is 45. Only tags after a throw.</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>25be4ee7-4347-444c-aa23-e7a83b659b9a</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
+      <c r="AC85" t="inlineStr">
         <is>
           <t>b3148b12-d240-42d2-bc74-cdad38408d24</t>
         </is>
@@ -8226,46 +8277,41 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Konvict Kick</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Konvict Kick</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8283,35 +8329,40 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="V86" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>ced50506-63d0-4a52-90ed-a4f805e17f32</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
+      <c r="AC86" t="inlineStr">
         <is>
           <t>2e623a96-be88-4870-b092-5e13335674c8</t>
         </is>
@@ -8328,46 +8379,41 @@
           <t>SS+4</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Animal Sweep</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Animal Sweep</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>-43</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>-43</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8385,40 +8431,45 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="V87" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>a5936aac-61c2-42f6-aaae-bd425f5a66a6</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
+      <c r="AC87" t="inlineStr">
         <is>
           <t>543157db-f8a1-4fe4-ba8a-49460227cd98</t>
         </is>
@@ -8435,97 +8486,97 @@
           <t>db+4</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Animal Kick</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Animal Kick</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>-29</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>-29</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="V88" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>Follow up with the Lunge Animal Kick extentions.</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>0717183d-ced3-42b2-9367-b2b84ab6e45e</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
+      <c r="AC88" t="inlineStr">
         <is>
           <t>dfa38971-818f-43b5-a0fa-86496ef76298</t>
         </is>
@@ -8562,130 +8613,135 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F91" s="1" t="inlineStr">
+      <c r="G91" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
+      <c r="H91" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H91" s="1" t="inlineStr">
+      <c r="I91" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I91" s="1" t="inlineStr">
+      <c r="J91" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J91" s="1" t="inlineStr">
+      <c r="K91" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K91" s="1" t="inlineStr">
+      <c r="L91" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L91" s="1" t="inlineStr">
+      <c r="M91" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M91" s="1" t="inlineStr">
+      <c r="N91" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N91" s="1" t="inlineStr">
+      <c r="O91" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O91" s="1" t="inlineStr">
+      <c r="P91" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P91" s="1" t="inlineStr">
+      <c r="Q91" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q91" s="1" t="inlineStr">
+      <c r="R91" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R91" s="1" t="inlineStr">
+      <c r="S91" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S91" s="1" t="inlineStr">
+      <c r="T91" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T91" s="1" t="inlineStr">
+      <c r="U91" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U91" s="1" t="inlineStr">
+      <c r="V91" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V91" s="1" t="inlineStr">
+      <c r="W91" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W91" s="1" t="inlineStr">
+      <c r="X91" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X91" s="1" t="inlineStr">
+      <c r="Y91" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y91" s="1" t="inlineStr">
+      <c r="Z91" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z91" s="1" t="inlineStr">
+      <c r="AA91" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA91" s="1" t="inlineStr">
+      <c r="AB91" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB91" s="1" t="inlineStr">
+      <c r="AC91" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC91" s="1" t="inlineStr">
+      <c r="AD91" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD91" s="1" t="inlineStr">
+      <c r="AE91" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8702,36 +8758,31 @@
           <t>b+1</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Animal Gigaton Punch</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Animal Gigaton Punch</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8749,35 +8800,40 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="V92" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>9404733c-1b10-4997-b131-d7a9acfb5f99</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
+      <c r="AC92" t="inlineStr">
         <is>
           <t>60e6f946-4545-4b28-88d1-37930f167fb7</t>
         </is>
@@ -8814,130 +8870,135 @@
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="G95" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="H95" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H95" s="1" t="inlineStr">
+      <c r="I95" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I95" s="1" t="inlineStr">
+      <c r="J95" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J95" s="1" t="inlineStr">
+      <c r="K95" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K95" s="1" t="inlineStr">
+      <c r="L95" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L95" s="1" t="inlineStr">
+      <c r="M95" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M95" s="1" t="inlineStr">
+      <c r="N95" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N95" s="1" t="inlineStr">
+      <c r="O95" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O95" s="1" t="inlineStr">
+      <c r="P95" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="Q95" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q95" s="1" t="inlineStr">
+      <c r="R95" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R95" s="1" t="inlineStr">
+      <c r="S95" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S95" s="1" t="inlineStr">
+      <c r="T95" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T95" s="1" t="inlineStr">
+      <c r="U95" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U95" s="1" t="inlineStr">
+      <c r="V95" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V95" s="1" t="inlineStr">
+      <c r="W95" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W95" s="1" t="inlineStr">
+      <c r="X95" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X95" s="1" t="inlineStr">
+      <c r="Y95" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y95" s="1" t="inlineStr">
+      <c r="Z95" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z95" s="1" t="inlineStr">
+      <c r="AA95" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA95" s="1" t="inlineStr">
+      <c r="AB95" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB95" s="1" t="inlineStr">
+      <c r="AC95" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC95" s="1" t="inlineStr">
+      <c r="AD95" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD95" s="1" t="inlineStr">
+      <c r="AE95" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
